--- a/data/trans_orig/P1401-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1401-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cáncer en 2012</t>
+          <t>Población con diagnóstico de cáncer en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>16807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>286117</t>
+          <t>285351</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293835</t>
+          <t>293793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270051</t>
+          <t>270438</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283982</t>
+          <t>283318</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561923</t>
+          <t>561861</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575684</t>
+          <t>575949</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19461</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496517</t>
+          <t>496107</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504540</t>
+          <t>504536</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>508680</t>
+          <t>509535</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521524</t>
+          <t>521545</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1009831</t>
+          <t>1009000</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1024841</t>
+          <t>1024336</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13815</t>
+          <t>15577</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22710</t>
+          <t>21787</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310231</t>
+          <t>308469</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321978</t>
+          <t>321945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327642</t>
+          <t>328581</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338887</t>
+          <t>338897</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>642356</t>
+          <t>643279</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658726</t>
+          <t>658723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>20004</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24744</t>
+          <t>24809</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>364919</t>
+          <t>365969</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373018</t>
+          <t>373029</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>369221</t>
+          <t>368947</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>383037</t>
+          <t>383246</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>738189</t>
+          <t>738124</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>754285</t>
+          <t>754865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>15389</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>970</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>18399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198023</t>
+          <t>197229</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210573</t>
+          <t>211446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>208481</t>
+          <t>208496</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218634</t>
+          <t>218621</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>411937</t>
+          <t>413810</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428008</t>
+          <t>428206</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9545</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13672</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264436</t>
+          <t>264222</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272913</t>
+          <t>272916</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>268650</t>
+          <t>269783</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277088</t>
+          <t>277097</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>538405</t>
+          <t>537554</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>548969</t>
+          <t>548922</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>11032</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>11217</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30489</t>
+          <t>30225</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15048</t>
+          <t>15155</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34592</t>
+          <t>34808</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>652573</t>
+          <t>651756</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>660854</t>
+          <t>660896</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>663364</t>
+          <t>663628</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>682846</t>
+          <t>682636</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1322049</t>
+          <t>1321833</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1341593</t>
+          <t>1341486</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14427</t>
+          <t>14195</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7487</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22979</t>
+          <t>21996</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12740</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32681</t>
+          <t>30719</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764671</t>
+          <t>764903</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775927</t>
+          <t>775968</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>799599</t>
+          <t>800582</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>815226</t>
+          <t>815091</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1568995</t>
+          <t>1570957</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1588936</t>
+          <t>1588677</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27811</t>
+          <t>27339</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54389</t>
+          <t>53228</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,74 +3491,74 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>71617</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>56327</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>93964</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>110782</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>89974</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>135408</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>1,59%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>71617</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>55781</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>90732</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>110782</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>90381</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>136569</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
           <t>1,29%</t>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3372390</t>
+          <t>3373551</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3398968</t>
+          <t>3399440</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,77 +3604,77 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3232</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3483481</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3461134</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3498771</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>97,36%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>6405</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6871095</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6846469</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6891903</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>98,41%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3232</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3483481</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>3464366</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3499317</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>6405</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6871095</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6845308</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6891496</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cáncer en 2016</t>
+          <t>Población con diagnóstico de cáncer en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13073</t>
+          <t>12814</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>14590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>289884</t>
+          <t>289083</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275630</t>
+          <t>275889</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285865</t>
+          <t>285753</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>568075</t>
+          <t>567874</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578849</t>
+          <t>578783</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,49 +4413,49 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4479</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1148</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10835</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>2,07%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4479</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10810</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>15474</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>492158</t>
+          <t>491767</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501547</t>
+          <t>501544</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,47 +4526,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,79%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>518605</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>512249</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>521936</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>97,93%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>518605</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>512274</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>522004</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1009202</t>
+          <t>1010185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1021442</t>
+          <t>1021600</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11617</t>
+          <t>10998</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6256</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23510</t>
+          <t>24399</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29552</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306948</t>
+          <t>307567</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316572</t>
+          <t>316641</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>312799</t>
+          <t>311910</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329939</t>
+          <t>330053</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>625322</t>
+          <t>626744</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644182</t>
+          <t>644675</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>11990</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19695</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27950</t>
+          <t>27122</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>358515</t>
+          <t>357974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367956</t>
+          <t>367934</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>367588</t>
+          <t>366930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>382063</t>
+          <t>382115</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>729297</t>
+          <t>730125</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>747324</t>
+          <t>747267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>983</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>9337</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203859</t>
+          <t>203236</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210327</t>
+          <t>210293</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>212461</t>
+          <t>212916</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>420740</t>
+          <t>420471</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428832</t>
+          <t>428825</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258756</t>
+          <t>258314</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266650</t>
+          <t>267084</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>529035</t>
+          <t>529211</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26560</t>
+          <t>25991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12819</t>
+          <t>13188</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31511</t>
+          <t>33476</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>646169</t>
+          <t>646362</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>654759</t>
+          <t>654779</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>664734</t>
+          <t>665303</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>682441</t>
+          <t>682561</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1316341</t>
+          <t>1314376</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1335033</t>
+          <t>1334664</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11940</t>
+          <t>14393</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28318</t>
+          <t>28034</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14435</t>
+          <t>15327</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34999</t>
+          <t>34968</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>766643</t>
+          <t>764190</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776864</t>
+          <t>776667</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>797849</t>
+          <t>798133</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>815553</t>
+          <t>816238</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1569751</t>
+          <t>1569782</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1590315</t>
+          <t>1589423</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20528</t>
+          <t>20040</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40577</t>
+          <t>41430</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>55598</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>90909</t>
+          <t>94528</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>81462</t>
+          <t>82250</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>123133</t>
+          <t>122264</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3353773</t>
+          <t>3352920</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3373822</t>
+          <t>3374310</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3453633</t>
+          <t>3450014</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3488944</t>
+          <t>3489436</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6815759</t>
+          <t>6816628</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6857430</t>
+          <t>6856642</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cáncer en 2023</t>
+          <t>Población con diagnóstico de cáncer en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>11087</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>304268</t>
+          <t>304337</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310656</t>
+          <t>310702</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283034</t>
+          <t>282599</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288174</t>
+          <t>288079</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>589864</t>
+          <t>589990</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>597738</t>
+          <t>598191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19444</t>
+          <t>19746</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13973</t>
+          <t>13305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28389</t>
+          <t>27688</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>497085</t>
+          <t>496783</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>511643</t>
+          <t>511837</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500318</t>
+          <t>500986</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509931</t>
+          <t>510371</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1002430</t>
+          <t>1003131</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1019274</t>
+          <t>1019324</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11655</t>
+          <t>11674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>13798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10658</t>
+          <t>10668</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23212</t>
+          <t>23251</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304395</t>
+          <t>304376</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312873</t>
+          <t>312552</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>334103</t>
+          <t>335330</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>343436</t>
+          <t>343648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>641966</t>
+          <t>641927</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>654520</t>
+          <t>654510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>11474</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>16583</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25171</t>
+          <t>24006</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>300663</t>
+          <t>301083</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309998</t>
+          <t>309980</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>459092</t>
+          <t>459135</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470254</t>
+          <t>469952</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>763103</t>
+          <t>764268</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>777307</t>
+          <t>777834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171036</t>
+          <t>170373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>176801</t>
+          <t>176587</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196713</t>
+          <t>196825</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203063</t>
+          <t>203269</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369607</t>
+          <t>369728</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>378605</t>
+          <t>378768</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>12809</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9213</t>
+          <t>9628</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8830</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257099</t>
+          <t>256827</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265380</t>
+          <t>265222</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>247174</t>
+          <t>246759</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>253322</t>
+          <t>253195</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>505948</t>
+          <t>506436</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>517193</t>
+          <t>516947</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>9948</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25479</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16560</t>
+          <t>16874</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38827</t>
+          <t>39408</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>594923</t>
+          <t>595408</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609800</t>
+          <t>610454</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>829377</t>
+          <t>828196</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>841934</t>
+          <t>841953</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1428160</t>
+          <t>1427579</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1450427</t>
+          <t>1450113</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24149</t>
+          <t>23856</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16229</t>
+          <t>15725</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30376</t>
+          <t>30426</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22846</t>
+          <t>22337</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50037</t>
+          <t>49645</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>903951</t>
+          <t>904244</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>922920</t>
+          <t>922716</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>685016</t>
+          <t>684966</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>699163</t>
+          <t>699667</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1593455</t>
+          <t>1593847</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1620646</t>
+          <t>1621155</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51219</t>
+          <t>52962</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>86048</t>
+          <t>85695</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>62072</t>
+          <t>60692</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>92266</t>
+          <t>93196</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>124444</t>
+          <t>123640</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>170844</t>
+          <t>170753</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3367410</t>
+          <t>3367763</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3402239</t>
+          <t>3400496</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3562756</t>
+          <t>3561826</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3592950</t>
+          <t>3594330</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6937636</t>
+          <t>6937727</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6984036</t>
+          <t>6984840</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1401-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1401-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16807</t>
+          <t>16226</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20164</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285351</t>
+          <t>285887</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293793</t>
+          <t>293831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270438</t>
+          <t>271019</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283318</t>
+          <t>284025</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561861</t>
+          <t>561819</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575949</t>
+          <t>575803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14230</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20292</t>
+          <t>19337</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496107</t>
+          <t>496610</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504536</t>
+          <t>504538</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509535</t>
+          <t>509201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521545</t>
+          <t>521551</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1009000</t>
+          <t>1009955</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1024336</t>
+          <t>1025029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15577</t>
+          <t>15550</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12439</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21787</t>
+          <t>22658</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308469</t>
+          <t>308496</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321945</t>
+          <t>321950</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328581</t>
+          <t>328363</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338897</t>
+          <t>338944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643279</t>
+          <t>642408</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658723</t>
+          <t>658824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20004</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24809</t>
+          <t>24183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>365969</t>
+          <t>366060</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373029</t>
+          <t>373049</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>368947</t>
+          <t>368539</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>383246</t>
+          <t>383080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>738124</t>
+          <t>738750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>754865</t>
+          <t>754719</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15389</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>960</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18399</t>
+          <t>19532</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197229</t>
+          <t>198219</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211446</t>
+          <t>211462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>208496</t>
+          <t>208990</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218621</t>
+          <t>218631</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>413810</t>
+          <t>412677</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428206</t>
+          <t>428295</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>10383</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>14630</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264222</t>
+          <t>263598</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272916</t>
+          <t>272915</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269783</t>
+          <t>269702</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277097</t>
+          <t>277091</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>537554</t>
+          <t>537447</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>548922</t>
+          <t>548930</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11032</t>
+          <t>12025</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>30659</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15155</t>
+          <t>15795</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34808</t>
+          <t>36644</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>651756</t>
+          <t>650763</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>660896</t>
+          <t>660827</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>663628</t>
+          <t>663194</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>682636</t>
+          <t>682127</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1321833</t>
+          <t>1319997</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1341486</t>
+          <t>1340846</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21996</t>
+          <t>22897</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30719</t>
+          <t>32910</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764903</t>
+          <t>764099</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775968</t>
+          <t>775946</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>800582</t>
+          <t>799681</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>815091</t>
+          <t>815322</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1570957</t>
+          <t>1568766</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1588677</t>
+          <t>1588061</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>28645</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53228</t>
+          <t>54935</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>56327</t>
+          <t>54850</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>93964</t>
+          <t>88816</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>89974</t>
+          <t>91287</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>135408</t>
+          <t>134369</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3373551</t>
+          <t>3371844</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3399440</t>
+          <t>3398134</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3461134</t>
+          <t>3466282</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3498771</t>
+          <t>3500248</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6846469</t>
+          <t>6847508</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6891903</t>
+          <t>6890590</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12814</t>
+          <t>13167</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3681</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14590</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>289083</t>
+          <t>288405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275889</t>
+          <t>275536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285753</t>
+          <t>285832</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567874</t>
+          <t>567527</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578783</t>
+          <t>578611</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>9457</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,47 +4413,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4479</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11220</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4479</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1148</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10835</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15474</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491767</t>
+          <t>493118</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501544</t>
+          <t>501545</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,49 +4526,49 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>99,8%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>518605</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>511864</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>522010</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>99,79%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>518605</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>512249</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>521936</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,78%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>951</t>
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1010185</t>
+          <t>1009456</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1021600</t>
+          <t>1021537</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24399</t>
+          <t>23924</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>30274</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307567</t>
+          <t>307448</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316641</t>
+          <t>316638</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>311910</t>
+          <t>312385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330053</t>
+          <t>329687</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>626744</t>
+          <t>624600</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644675</t>
+          <t>644457</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>11698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>20619</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9980</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27122</t>
+          <t>27854</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>357974</t>
+          <t>358266</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367934</t>
+          <t>367914</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>366930</t>
+          <t>366664</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>382115</t>
+          <t>381357</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>730125</t>
+          <t>729393</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>747267</t>
+          <t>747483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9337</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210293</t>
+          <t>210337</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>212916</t>
+          <t>213602</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>420471</t>
+          <t>420289</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428825</t>
+          <t>428822</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258314</t>
+          <t>259911</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>267084</t>
+          <t>266541</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>529211</t>
+          <t>527915</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9549</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25991</t>
+          <t>26131</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13188</t>
+          <t>12361</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33476</t>
+          <t>31190</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>646362</t>
+          <t>647009</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>654779</t>
+          <t>654770</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>665303</t>
+          <t>665163</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>682561</t>
+          <t>682146</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1314376</t>
+          <t>1316662</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1334664</t>
+          <t>1335491</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>27828</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15327</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34968</t>
+          <t>34796</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764190</t>
+          <t>765983</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776667</t>
+          <t>776758</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>798133</t>
+          <t>798339</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>816238</t>
+          <t>816065</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1569782</t>
+          <t>1569954</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1589423</t>
+          <t>1589894</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20040</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41430</t>
+          <t>42386</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>53433</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>94528</t>
+          <t>90386</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>82250</t>
+          <t>82952</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>122264</t>
+          <t>123352</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3352920</t>
+          <t>3351964</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3374310</t>
+          <t>3373149</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3450014</t>
+          <t>3454156</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3489436</t>
+          <t>3491109</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6816628</t>
+          <t>6815540</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6856642</t>
+          <t>6855940</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -7373,22 +7373,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>771</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7408,32 +7408,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>7454</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7443,32 +7443,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3371</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11087</t>
+          <t>11638</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -7486,27 +7486,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>308756</t>
+          <t>315757</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>304337</t>
+          <t>311607</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310702</t>
+          <t>318074</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7521,32 +7521,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>286096</t>
+          <t>312260</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282599</t>
+          <t>308607</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288079</t>
+          <t>314234</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7556,32 +7556,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>594850</t>
+          <t>628018</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>589990</t>
+          <t>623268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>598191</t>
+          <t>631535</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -7599,17 +7599,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7634,17 +7634,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7716,32 +7716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19746</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7751,32 +7751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>13762</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7786,22 +7786,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18457</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>12068</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27688</t>
+          <t>28144</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -7829,32 +7829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>506065</t>
+          <t>518373</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496783</t>
+          <t>509483</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>511837</t>
+          <t>524147</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7864,32 +7864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>506297</t>
+          <t>537701</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500986</t>
+          <t>532047</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510371</t>
+          <t>541351</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7899,27 +7899,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1012362</t>
+          <t>1056075</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1003131</t>
+          <t>1046384</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1019324</t>
+          <t>1062460</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7942,17 +7942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>516529</t>
+          <t>528718</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>516529</t>
+          <t>528718</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>516529</t>
+          <t>528718</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8012,17 +8012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1030819</t>
+          <t>1074528</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1030819</t>
+          <t>1074528</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1030819</t>
+          <t>1074528</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8059,32 +8059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11674</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8094,32 +8094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13798</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8129,17 +8129,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15843</t>
+          <t>16022</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23251</t>
+          <t>23591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -8172,32 +8172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>309540</t>
+          <t>309562</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304376</t>
+          <t>304783</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312552</t>
+          <t>312781</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8207,32 +8207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>339795</t>
+          <t>346791</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>335330</t>
+          <t>341505</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>343648</t>
+          <t>350608</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8242,17 +8242,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>649335</t>
+          <t>656353</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>641927</t>
+          <t>648784</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>654510</t>
+          <t>661564</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8355,17 +8355,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8402,32 +8402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11474</t>
+          <t>14096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10746</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16583</t>
+          <t>17631</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8472,32 +8472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>19532</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10440</t>
+          <t>13623</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24006</t>
+          <t>28204</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -8515,32 +8515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>306692</t>
+          <t>365825</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>301083</t>
+          <t>359049</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309980</t>
+          <t>369786</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8550,32 +8550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>464972</t>
+          <t>409749</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>459135</t>
+          <t>404330</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>469952</t>
+          <t>414238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8585,32 +8585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>771663</t>
+          <t>775575</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>764268</t>
+          <t>766903</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>777834</t>
+          <t>781484</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -8628,17 +8628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8745,32 +8745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>8944</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8780,32 +8780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>11687</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8815,32 +8815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7861</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>17845</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -8858,32 +8858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>174370</t>
+          <t>201012</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170373</t>
+          <t>196721</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>176587</t>
+          <t>203642</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8893,32 +8893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>200449</t>
+          <t>218738</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196825</t>
+          <t>214728</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203269</t>
+          <t>221624</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8928,32 +8928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>374819</t>
+          <t>419750</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369728</t>
+          <t>414235</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>378768</t>
+          <t>423724</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207887</t>
+          <t>226415</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207887</t>
+          <t>226415</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207887</t>
+          <t>226415</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386629</t>
+          <t>432080</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386629</t>
+          <t>432080</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386629</t>
+          <t>432080</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9088,32 +9088,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9123,17 +9123,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9628</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -9158,32 +9158,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19587</t>
+          <t>19263</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -9201,32 +9201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>261790</t>
+          <t>262953</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256827</t>
+          <t>258152</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265222</t>
+          <t>266222</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9236,17 +9236,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>250769</t>
+          <t>257345</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>246759</t>
+          <t>253197</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>253195</t>
+          <t>259875</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9271,32 +9271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>512559</t>
+          <t>520297</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>506436</t>
+          <t>514543</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>516947</t>
+          <t>524714</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -9314,17 +9314,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9349,17 +9349,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9431,67 +9431,67 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>18458</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24994</t>
+          <t>28394</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>12292</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>7484</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>18582</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>10638</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>4633</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>18390</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9501,32 +9501,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>27355</t>
+          <t>30750</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16874</t>
+          <t>22425</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39408</t>
+          <t>41611</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -9544,67 +9544,67 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>603685</t>
+          <t>696068</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>595408</t>
+          <t>686132</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>610454</t>
+          <t>703287</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>756269</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>749979</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>761077</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>98,4%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>835948</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>828196</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>841953</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9614,32 +9614,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1439632</t>
+          <t>1452337</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1427579</t>
+          <t>1441476</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1450113</t>
+          <t>1460662</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -9657,17 +9657,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>620402</t>
+          <t>714526</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>620402</t>
+          <t>714526</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>620402</t>
+          <t>714526</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>846586</t>
+          <t>768561</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>846586</t>
+          <t>768561</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>846586</t>
+          <t>768561</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1466987</t>
+          <t>1483087</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1466987</t>
+          <t>1483087</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1466987</t>
+          <t>1483087</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9774,102 +9774,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23856</t>
+          <t>24890</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>25384</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>18017</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>34216</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>41842</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>32508</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>55201</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>2,57%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>22634</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>15725</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>30426</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>37050</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>22337</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>49645</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -9887,102 +9887,102 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>913684</t>
+          <t>780946</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>904244</t>
+          <t>772514</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>922716</t>
+          <t>787276</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>805225</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>796393</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>812592</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>95,88%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1764</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1586171</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1572812</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1595505</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>97,43%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1023</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>692758</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>684966</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>699667</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>95,75%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1764</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1606442</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1593847</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1621155</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>97,75%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -10000,17 +10000,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928100</t>
+          <t>797404</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928100</t>
+          <t>797404</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928100</t>
+          <t>797404</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643492</t>
+          <t>1628013</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643492</t>
+          <t>1628013</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643492</t>
+          <t>1628013</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10117,32 +10117,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>68877</t>
+          <t>74507</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52962</t>
+          <t>58261</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>85695</t>
+          <t>90426</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10152,32 +10152,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>77940</t>
+          <t>84818</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>60692</t>
+          <t>71138</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>93196</t>
+          <t>98188</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10187,32 +10187,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>146817</t>
+          <t>159325</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>123640</t>
+          <t>140385</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>170753</t>
+          <t>181701</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -10230,32 +10230,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3384581</t>
+          <t>3450497</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3367763</t>
+          <t>3434578</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3400496</t>
+          <t>3466743</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10265,32 +10265,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3577082</t>
+          <t>3644079</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3561826</t>
+          <t>3630709</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3594330</t>
+          <t>3657759</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10300,32 +10300,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6961663</t>
+          <t>7094576</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6937727</t>
+          <t>7072200</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6984840</t>
+          <t>7113516</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -10343,17 +10343,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3453458</t>
+          <t>3525004</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3453458</t>
+          <t>3525004</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3453458</t>
+          <t>3525004</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3655022</t>
+          <t>3728897</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3655022</t>
+          <t>3728897</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3655022</t>
+          <t>3728897</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10413,17 +10413,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7108480</t>
+          <t>7253901</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7108480</t>
+          <t>7253901</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7108480</t>
+          <t>7253901</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
